--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Casademont Zaragoza.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Casademont Zaragoza.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5052</v>
+        <v>26.0381</v>
       </c>
       <c r="E2" t="n">
-        <v>21.2265</v>
+        <v>16.2776</v>
       </c>
       <c r="F2" t="n">
-        <v>6.278599999999999</v>
+        <v>9.7605</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5085</v>
+        <v>4.802700000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>19.0872</v>
+        <v>22.0865</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.5787</v>
+        <v>-17.2838</v>
       </c>
       <c r="J2" t="n">
-        <v>46.1366</v>
+        <v>49.2768</v>
       </c>
       <c r="K2" t="n">
-        <v>40.5877</v>
+        <v>46.8616</v>
       </c>
       <c r="L2" t="n">
-        <v>5.548999999999999</v>
+        <v>2.4148</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.6281</v>
+        <v>-44.4741</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.5008</v>
+        <v>-24.7754</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.1274</v>
+        <v>-19.6988</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4534999999999996</v>
+        <v>1.5936</v>
       </c>
       <c r="Q2" t="n">
-        <v>-55.5742</v>
+        <v>-70.5659</v>
       </c>
       <c r="R2" t="n">
-        <v>55.1204</v>
+        <v>72.1591</v>
       </c>
       <c r="S2" t="n">
-        <v>7.2518</v>
+        <v>8.565100000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1567000000000003</v>
+        <v>1.7685</v>
       </c>
       <c r="U2" t="n">
-        <v>7.4085</v>
+        <v>6.7966</v>
       </c>
       <c r="V2" t="n">
-        <v>9.1983</v>
+        <v>11.0767</v>
       </c>
       <c r="W2" t="n">
-        <v>30.8208</v>
+        <v>35.7979</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.6224</v>
+        <v>-24.721</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7473</v>
+        <v>11.003</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7956</v>
+        <v>6.358000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.951899999999999</v>
+        <v>4.645099999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-21.6248</v>
+        <v>-34.5586</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.535399999999999</v>
+        <v>-12.9839</v>
       </c>
       <c r="I3" t="n">
-        <v>-14.0895</v>
+        <v>-21.5746</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4195</v>
+        <v>-1.5306</v>
       </c>
       <c r="K3" t="n">
-        <v>10.927</v>
+        <v>8.9953</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.507199999999999</v>
+        <v>-10.5262</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.0443</v>
+        <v>-33.0281</v>
       </c>
       <c r="N3" t="n">
-        <v>-18.4622</v>
+        <v>-21.9793</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.5823</v>
+        <v>-11.0482</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.763500000000001</v>
+        <v>-8.649900000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.7371</v>
+        <v>-54.8592</v>
       </c>
       <c r="R3" t="n">
-        <v>36.974</v>
+        <v>46.2094</v>
       </c>
       <c r="S3" t="n">
-        <v>36.1942</v>
+        <v>46.1289</v>
       </c>
       <c r="T3" t="n">
-        <v>27.2387</v>
+        <v>35.0078</v>
       </c>
       <c r="U3" t="n">
-        <v>8.955500000000001</v>
+        <v>11.1207</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9419</v>
+        <v>8.0829</v>
       </c>
       <c r="W3" t="n">
-        <v>24.8747</v>
+        <v>27.74</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.9329</v>
+        <v>-19.6571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>G. OLASENI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>15.9062</v>
+        <v>4.0807</v>
       </c>
       <c r="E4" t="n">
-        <v>32.1649</v>
+        <v>4.293600000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-16.2589</v>
+        <v>-0.2128000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.4577</v>
+        <v>-0.6414000000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5094</v>
+        <v>4.6055</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.9671</v>
+        <v>-5.2468</v>
       </c>
       <c r="J4" t="n">
-        <v>34.074</v>
+        <v>6.3216</v>
       </c>
       <c r="K4" t="n">
-        <v>29.645</v>
+        <v>5.8005</v>
       </c>
       <c r="L4" t="n">
-        <v>4.429100000000001</v>
+        <v>0.5212</v>
       </c>
       <c r="M4" t="n">
-        <v>-45.5319</v>
+        <v>-6.963100000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.1356</v>
+        <v>-1.1949</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.3961</v>
+        <v>-5.7683</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.309699999999999</v>
+        <v>2.504</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60.7913</v>
+        <v>-5.9185</v>
       </c>
       <c r="R4" t="n">
-        <v>56.4816</v>
+        <v>8.4224</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.894299999999999</v>
+        <v>0.8132</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.779100000000001</v>
+        <v>0.7647999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.115</v>
+        <v>0.04840000000000011</v>
       </c>
       <c r="V4" t="n">
-        <v>39.5677</v>
+        <v>1.4051</v>
       </c>
       <c r="W4" t="n">
-        <v>64.6614</v>
+        <v>3.1254</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.0933</v>
+        <v>-1.7206</v>
       </c>
     </row>
     <row r="5">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1868</v>
+        <v>2.1841</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3602</v>
+        <v>1.3549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8266</v>
+        <v>0.8293</v>
       </c>
       <c r="G5" t="n">
-        <v>1.443</v>
+        <v>1.4418</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1284</v>
+        <v>1.126</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,19 +844,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1975</v>
+        <v>0.1976</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1975</v>
+        <v>0.1976</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2598</v>
+        <v>1.325199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2598</v>
+        <v>16.8292</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-15.5039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2598</v>
+        <v>-32.724</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2598</v>
+        <v>-0.6294999999999995</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-32.0949</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2598</v>
+        <v>24.4573</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2598</v>
+        <v>28.3683</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.911300000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-57.1814</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-28.9981</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-28.1838</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.4551000000000006</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-74.8908</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>74.4357</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-10.6865</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-7.038200000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-3.6478</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>45.191</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>74.30119999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-29.1102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LANGARITA</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1746</v>
+        <v>0.2586</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0173</v>
+        <v>0.2586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1746</v>
+        <v>0.2586</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0173</v>
+        <v>0.2586</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0173</v>
+        <v>0.2586</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.2586</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SAVKOV</t>
+          <t>L. LANGARITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5923</v>
+        <v>0.1752</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8559</v>
+        <v>0.0172</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.1579</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3145</v>
+        <v>0.1752</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>0.0172</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4718</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7864</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4718</v>
+        <v>0.1579</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1851</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1155</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. ALIAS</t>
+          <t>A. SAVKOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7454</v>
+        <v>-1.5911</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0795</v>
+        <v>-0.8593</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6659</v>
+        <v>-0.7318</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5235</v>
+        <v>-0.3159</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3449</v>
+        <v>0.1579</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1786</v>
+        <v>-0.4738</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0546</v>
+        <v>-0.7896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5782</v>
+        <v>0.4738</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3623</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2159</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3145</v>
+        <v>-0.1858</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3145</v>
+        <v>-0.1161</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>C. ALIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.426499999999999</v>
+        <v>-1.7456</v>
       </c>
       <c r="E10" t="n">
-        <v>4.7125</v>
+        <v>-1.0837</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.1389</v>
+        <v>-0.6618999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.3262</v>
+        <v>-0.5192</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.6926</v>
+        <v>-0.342</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6339000000000001</v>
+        <v>-0.1772</v>
       </c>
       <c r="J10" t="n">
-        <v>9.342499999999999</v>
+        <v>0.0545</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7285</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6141</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-23.6693</v>
+        <v>-0.5736</v>
       </c>
       <c r="N10" t="n">
-        <v>-16.4213</v>
+        <v>-0.3592</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.248099999999999</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>17.9201</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.8784</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>33.7982</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>3.0979</v>
+        <v>-0.3159</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3705</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2731</v>
+        <v>-0.3159</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.1177</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>6.8775</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.9951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0956</v>
+        <v>-3.0751</v>
       </c>
       <c r="E11" t="n">
-        <v>4.658700000000001</v>
+        <v>2.2951</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.754</v>
+        <v>-5.3701</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.2628</v>
+        <v>-24.1899</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.7288</v>
+        <v>-16.7888</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5339</v>
+        <v>-7.401400000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>4.272600000000001</v>
+        <v>5.6443</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3619</v>
+        <v>1.7599</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9107</v>
+        <v>3.8846</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.5351</v>
+        <v>-29.8345</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.0906</v>
+        <v>-18.5489</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.4448</v>
+        <v>-11.2861</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.5782</v>
+        <v>25.7228</v>
       </c>
       <c r="Q11" t="n">
-        <v>-21.776</v>
+        <v>-17.7553</v>
       </c>
       <c r="R11" t="n">
-        <v>15.1978</v>
+        <v>43.478</v>
       </c>
       <c r="S11" t="n">
-        <v>10.3249</v>
+        <v>5.5787</v>
       </c>
       <c r="T11" t="n">
-        <v>9.917400000000001</v>
+        <v>6.306500000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4076</v>
+        <v>-0.7277999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4204</v>
+        <v>-10.1855</v>
       </c>
       <c r="W11" t="n">
-        <v>12.2449</v>
+        <v>8.0997</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.8244</v>
+        <v>-18.285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2667</v>
+        <v>-4.055699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.317400000000001</v>
+        <v>4.315300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.5839</v>
+        <v>-8.370999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.822999999999999</v>
+        <v>-9.234500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>8.7043</v>
+        <v>-6.8083</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.8817</v>
+        <v>-2.4262</v>
       </c>
       <c r="J12" t="n">
-        <v>10.8752</v>
+        <v>4.0181</v>
       </c>
       <c r="K12" t="n">
-        <v>9.3452</v>
+        <v>1.1138</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5299</v>
+        <v>2.9043</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.0525</v>
+        <v>-13.2525</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6411</v>
+        <v>-7.9218</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.4114</v>
+        <v>-5.3309</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.9391</v>
+        <v>-6.6014</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.2393</v>
+        <v>-21.8526</v>
       </c>
       <c r="R12" t="n">
-        <v>9.3002</v>
+        <v>15.2513</v>
       </c>
       <c r="S12" t="n">
-        <v>12.6851</v>
+        <v>10.3638</v>
       </c>
       <c r="T12" t="n">
-        <v>11.3388</v>
+        <v>9.978300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3463</v>
+        <v>0.3853</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.8355</v>
+        <v>1.4162</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3428</v>
+        <v>12.1717</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.1782</v>
+        <v>-10.7553</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.5461</v>
+        <v>-5.5305</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7876</v>
+        <v>15.0717</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.3334</v>
+        <v>-20.6021</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1971</v>
+        <v>-8.787400000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9560999999999993</v>
+        <v>3.4602</v>
       </c>
       <c r="I13" t="n">
-        <v>3.241</v>
+        <v>-12.247</v>
       </c>
       <c r="J13" t="n">
-        <v>19.4366</v>
+        <v>11.638</v>
       </c>
       <c r="K13" t="n">
-        <v>10.0788</v>
+        <v>14.4121</v>
       </c>
       <c r="L13" t="n">
-        <v>9.357899999999999</v>
+        <v>-2.7739</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.2394</v>
+        <v>-20.4257</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.1228</v>
+        <v>-10.9522</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.1167</v>
+        <v>-9.473100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.4856</v>
+        <v>6.6015</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.5076</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>12.0221</v>
+        <v>20.2595</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.4929</v>
+        <v>13.099</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.4084</v>
+        <v>11.1713</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0845</v>
+        <v>1.9279</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7648</v>
+        <v>-16.4433</v>
       </c>
       <c r="W13" t="n">
-        <v>6.266900000000001</v>
+        <v>5.9207</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.031899999999999</v>
+        <v>-22.3641</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.7173</v>
+        <v>-9.236299999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2195</v>
+        <v>7.0718</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.4979</v>
+        <v>-16.3081</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.2968</v>
+        <v>1.6143</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.4785</v>
+        <v>8.209999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8179000000000001</v>
+        <v>-6.595199999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0324</v>
+        <v>10.8649</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.1145</v>
+        <v>9.264099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0822</v>
+        <v>1.6012</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2645</v>
+        <v>-9.2509</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3641</v>
+        <v>-1.0543</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9001</v>
+        <v>-8.1965</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.495</v>
+        <v>-7.2841</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.3513</v>
+        <v>-17.3</v>
       </c>
       <c r="R14" t="n">
-        <v>3.8561</v>
+        <v>10.0159</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5493</v>
+        <v>12.3565</v>
       </c>
       <c r="T14" t="n">
-        <v>4.449</v>
+        <v>10.9824</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8996</v>
+        <v>1.3742</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.4751</v>
+        <v>-15.9229</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.2852</v>
+        <v>2.5244</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1898</v>
+        <v>-18.4473</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.8651</v>
+        <v>-12.8961</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.3677</v>
+        <v>-11.4753</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4975</v>
+        <v>-1.421</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.5738</v>
+        <v>-6.5892</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.9953</v>
+        <v>-6.005</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5783999999999998</v>
+        <v>-0.5840999999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.8948</v>
+        <v>-4.9764</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.550199999999999</v>
+        <v>-5.6007</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6553999999999995</v>
+        <v>0.6242999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.679</v>
+        <v>-1.6128</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4451000000000001</v>
+        <v>-0.4042000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.234</v>
+        <v>-1.2084</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0416</v>
+        <v>-2.0488</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.7636</v>
+        <v>-4.7803</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.8487</v>
+        <v>-2.8592</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.4165</v>
+        <v>-2.421</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4322</v>
+        <v>-0.4382</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4012</v>
+        <v>-1.399</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1082</v>
+        <v>-2.1015</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.1294</v>
+        <v>-14.801</v>
       </c>
       <c r="E16" t="n">
-        <v>2.604</v>
+        <v>-6.069599999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.7332</v>
+        <v>-8.7316</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.9354</v>
+        <v>-6.606</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0335</v>
+        <v>-5.0766</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.9693</v>
+        <v>-1.5296</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8209</v>
+        <v>-1.1686</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6561</v>
+        <v>-2.3602</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.8349</v>
+        <v>1.1915</v>
       </c>
       <c r="M16" t="n">
-        <v>-16.7568</v>
+        <v>-5.4376</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.6228</v>
+        <v>-2.7166</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.1341</v>
+        <v>-2.7212</v>
       </c>
       <c r="P16" t="n">
-        <v>4.31</v>
+        <v>-2.7315</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.5685</v>
+        <v>-7.7395</v>
       </c>
       <c r="R16" t="n">
-        <v>15.8785</v>
+        <v>5.007899999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>7.9869</v>
+        <v>3.0886</v>
       </c>
       <c r="T16" t="n">
-        <v>5.4988</v>
+        <v>4.1422</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4885</v>
+        <v>-1.0535</v>
       </c>
       <c r="V16" t="n">
-        <v>-15.4905</v>
+        <v>-8.552100000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8528</v>
+        <v>-1.3037</v>
       </c>
       <c r="X16" t="n">
-        <v>-20.3432</v>
+        <v>-7.2483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.8321</v>
+        <v>-18.3084</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7204000000000006</v>
+        <v>-15.7712</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.1117</v>
+        <v>-2.5372</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8890000000000003</v>
+        <v>-8.109</v>
       </c>
       <c r="H17" t="n">
-        <v>2.096900000000001</v>
+        <v>-3.298</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.986</v>
+        <v>-4.811</v>
       </c>
       <c r="J17" t="n">
-        <v>12.2679</v>
+        <v>-2.5858</v>
       </c>
       <c r="K17" t="n">
-        <v>7.7245</v>
+        <v>0.5981999999999998</v>
       </c>
       <c r="L17" t="n">
-        <v>4.543399999999999</v>
+        <v>-3.1838</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.1569</v>
+        <v>-5.523199999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.6277</v>
+        <v>-3.8959</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.5293</v>
+        <v>-1.6272</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.5781</v>
+        <v>-5.4633</v>
       </c>
       <c r="Q17" t="n">
-        <v>-14.5174</v>
+        <v>-12.975</v>
       </c>
       <c r="R17" t="n">
-        <v>7.9392</v>
+        <v>7.5119</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.4157</v>
+        <v>-1.2727</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.2954</v>
+        <v>-2.3894</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.1202</v>
+        <v>1.1168</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.9494</v>
+        <v>-3.4637</v>
       </c>
       <c r="W17" t="n">
-        <v>3.8244</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-8.7736</v>
+        <v>-5.6427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.2923</v>
+        <v>-21.6613</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.5759</v>
+        <v>-3.625800000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7164</v>
+        <v>-18.0353</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.097799999999999</v>
+        <v>-4.7069</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3104</v>
+        <v>-1.4344</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.7873</v>
+        <v>-3.272500000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4426</v>
+        <v>10.0447</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6632999999999999</v>
+        <v>4.8611</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.1059</v>
+        <v>5.183599999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.6554</v>
+        <v>-14.7516</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.9737</v>
+        <v>-6.2956</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6816</v>
+        <v>-8.456</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.444100000000001</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q18" t="n">
-        <v>-12.9296</v>
+        <v>-14.7961</v>
       </c>
       <c r="R18" t="n">
-        <v>7.4855</v>
+        <v>10.0159</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2668</v>
+        <v>-5.0777</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.3893</v>
+        <v>-2.6876</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1225</v>
+        <v>-2.3898</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.4838</v>
+        <v>-7.0966</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>3.8132</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.6692</v>
+        <v>-10.9097</v>
       </c>
     </row>
     <row r="19">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.1338</v>
+        <v>-23.7716</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6476999999999999</v>
+        <v>-1.0589</v>
       </c>
       <c r="F19" t="n">
-        <v>-23.7816</v>
+        <v>-22.7131</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.1098</v>
+        <v>-17.9055</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2857000000000001</v>
+        <v>-0.6828000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.3953</v>
+        <v>-17.2228</v>
       </c>
       <c r="J19" t="n">
-        <v>11.9276</v>
+        <v>10.7556</v>
       </c>
       <c r="K19" t="n">
-        <v>11.5902</v>
+        <v>11.3054</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3373</v>
+        <v>-0.5494999999999995</v>
       </c>
       <c r="M19" t="n">
-        <v>-28.0374</v>
+        <v>-28.6613</v>
       </c>
       <c r="N19" t="n">
-        <v>-11.3045</v>
+        <v>-11.9882</v>
       </c>
       <c r="O19" t="n">
-        <v>-16.7328</v>
+        <v>-16.6726</v>
       </c>
       <c r="P19" t="n">
-        <v>9.073500000000001</v>
+        <v>9.788399999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-14.7441</v>
+        <v>-14.796</v>
       </c>
       <c r="R19" t="n">
-        <v>23.8175</v>
+        <v>24.5844</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.1963</v>
+        <v>-4.7962</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.228</v>
+        <v>-1.6917</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.9685</v>
+        <v>-3.1047</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.9011</v>
+        <v>-10.8575</v>
       </c>
       <c r="W19" t="n">
-        <v>4.6922</v>
+        <v>4.6736</v>
       </c>
       <c r="X19" t="n">
-        <v>-15.5933</v>
+        <v>-15.531</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>-23.3167</v>
+        <v>-35.7781</v>
       </c>
       <c r="E20" t="n">
-        <v>-20.2453</v>
+        <v>-14.995</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0716</v>
+        <v>-20.7828</v>
       </c>
       <c r="G20" t="n">
-        <v>10.4611</v>
+        <v>-9.177099999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1929</v>
+        <v>-1.9329</v>
       </c>
       <c r="I20" t="n">
-        <v>8.2685</v>
+        <v>-7.244299999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>29.4856</v>
+        <v>17.1451</v>
       </c>
       <c r="K20" t="n">
-        <v>14.1208</v>
+        <v>11.001</v>
       </c>
       <c r="L20" t="n">
-        <v>15.3645</v>
+        <v>6.1441</v>
       </c>
       <c r="M20" t="n">
-        <v>-19.0241</v>
+        <v>-26.3221</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.9277</v>
+        <v>-12.9341</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.0964</v>
+        <v>-13.388</v>
       </c>
       <c r="P20" t="n">
-        <v>-35.1592</v>
+        <v>-11.6093</v>
       </c>
       <c r="Q20" t="n">
-        <v>-70.7718</v>
+        <v>-33.9172</v>
       </c>
       <c r="R20" t="n">
-        <v>35.6129</v>
+        <v>22.308</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.5058</v>
+        <v>-12.4369</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.525399999999999</v>
+        <v>-6.7957</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.9804</v>
+        <v>-5.6411</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8869</v>
+        <v>-2.5546</v>
       </c>
       <c r="W20" t="n">
-        <v>29.5669</v>
+        <v>8.573</v>
       </c>
       <c r="X20" t="n">
-        <v>-16.6799</v>
+        <v>-11.1277</v>
       </c>
     </row>
     <row r="21">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
-        <v>-26.3775</v>
+        <v>-36.4325</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.4353</v>
+        <v>-37.3126</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.942399999999999</v>
+        <v>0.8805000000000004</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.241099999999999</v>
+        <v>-22.3893</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.0915</v>
+        <v>-12.9721</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8497</v>
+        <v>-9.417100000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>23.5616</v>
+        <v>16.5917</v>
       </c>
       <c r="K21" t="n">
-        <v>12.2089</v>
+        <v>10.5903</v>
       </c>
       <c r="L21" t="n">
-        <v>11.3528</v>
+        <v>6.0013</v>
       </c>
       <c r="M21" t="n">
-        <v>-30.8027</v>
+        <v>-38.9806</v>
       </c>
       <c r="N21" t="n">
-        <v>-21.2997</v>
+        <v>-23.5622</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.502600000000001</v>
+        <v>-15.4188</v>
       </c>
       <c r="P21" t="n">
-        <v>-21.5491</v>
+        <v>-17.5274</v>
       </c>
       <c r="Q21" t="n">
-        <v>-59.6573</v>
+        <v>-68.517</v>
       </c>
       <c r="R21" t="n">
-        <v>38.108</v>
+        <v>50.9898</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.984</v>
+        <v>-5.507099999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.8832</v>
+        <v>-7.206500000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1005000000000007</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>9.396799999999999</v>
+        <v>8.991</v>
       </c>
       <c r="W21" t="n">
-        <v>18.5436</v>
+        <v>21.8191</v>
       </c>
       <c r="X21" t="n">
-        <v>-9.146699999999999</v>
+        <v>-12.8282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,148 +2122,226 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>-47.6062</v>
+        <v>-38.2562</v>
       </c>
       <c r="E22" t="n">
-        <v>-23.8259</v>
+        <v>-27.1037</v>
       </c>
       <c r="F22" t="n">
-        <v>-23.7803</v>
+        <v>-11.1524</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.8088</v>
+        <v>11.9723</v>
       </c>
       <c r="H22" t="n">
-        <v>-17.0422</v>
+        <v>5.832199999999998</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2333</v>
+        <v>6.1403</v>
       </c>
       <c r="J22" t="n">
-        <v>16.5226</v>
+        <v>38.2207</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9217</v>
+        <v>19.5094</v>
       </c>
       <c r="L22" t="n">
-        <v>11.6002</v>
+        <v>18.7113</v>
       </c>
       <c r="M22" t="n">
-        <v>-31.331</v>
+        <v>-26.2483</v>
       </c>
       <c r="N22" t="n">
-        <v>-21.9639</v>
+        <v>-13.6768</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.366900000000001</v>
+        <v>-12.5712</v>
       </c>
       <c r="P22" t="n">
-        <v>-8.3927</v>
+        <v>-43.4776</v>
       </c>
       <c r="Q22" t="n">
-        <v>-50.8108</v>
+        <v>-89.2316</v>
       </c>
       <c r="R22" t="n">
-        <v>42.4178</v>
+        <v>45.7538</v>
       </c>
       <c r="S22" t="n">
-        <v>-22.8879</v>
+        <v>-13.5404</v>
       </c>
       <c r="T22" t="n">
-        <v>-12.1309</v>
+        <v>-7.803900000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-10.7572</v>
+        <v>-5.7364</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.516999999999999</v>
+        <v>6.789400000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>22.5929</v>
+        <v>31.7111</v>
       </c>
       <c r="X22" t="n">
-        <v>-24.11</v>
+        <v>-24.9216</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>M. SPISSU</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Casademont Zaragoza</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-40.5228</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-9.664300000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-30.8583</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-9.8011</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-14.8246</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.023200000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.4057</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12.0572</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.3482</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-44.2068</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-26.8817</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-17.3253</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-6.3736</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-64.8751</v>
+      </c>
+      <c r="R23" t="n">
+        <v>58.5016</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-25.0244</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-10.733</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-14.2913</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6762999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>31.5383</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-30.8616</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Casademont Zaragoza</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>28</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-161.1631</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-10.77320000000002</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-150.3896</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-99.59490000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-26.7908</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-72.8051</v>
-      </c>
-      <c r="J23" t="n">
-        <v>216.1326</v>
-      </c>
-      <c r="K23" t="n">
-        <v>160.0032</v>
-      </c>
-      <c r="L23" t="n">
-        <v>56.1294</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-315.7284</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-186.7941</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-128.9342</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-82.7931</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-479.7524999999999</v>
-      </c>
-      <c r="R23" t="n">
-        <v>396.9585999999999</v>
-      </c>
-      <c r="S23" t="n">
-        <v>11.2956</v>
-      </c>
-      <c r="T23" t="n">
-        <v>17.5307</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-6.234799999999999</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.929500000000001</v>
-      </c>
-      <c r="W23" t="n">
-        <v>235.3153</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-225.3848</v>
+      <c r="C24" t="n">
+        <v>34</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-222.5974</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-54.8764</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-167.7201</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-175.9901</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-38.0248</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-137.965</v>
+      </c>
+      <c r="J24" t="n">
+        <v>229.4739</v>
+      </c>
+      <c r="K24" t="n">
+        <v>179.6404</v>
+      </c>
+      <c r="L24" t="n">
+        <v>49.8333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-405.4647999999999</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-217.6656</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-187.7991</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-71.7025</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-589.5662</v>
+      </c>
+      <c r="R24" t="n">
+        <v>517.8638</v>
+      </c>
+      <c r="S24" t="n">
+        <v>18.4886</v>
+      </c>
+      <c r="T24" t="n">
+        <v>31.28510000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-12.7951</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.608599999999997</v>
+      </c>
+      <c r="W24" t="n">
+        <v>273.9317</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-267.3224</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Casademont Zaragoza.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Casademont Zaragoza.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>26.0381</v>
+        <v>22.6268</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2776</v>
+        <v>16.0761</v>
       </c>
       <c r="F2" t="n">
-        <v>9.7605</v>
+        <v>6.550800000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.802700000000002</v>
@@ -610,13 +610,13 @@
         <v>72.1591</v>
       </c>
       <c r="S2" t="n">
-        <v>8.565100000000001</v>
+        <v>5.153799999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7685</v>
+        <v>1.5669</v>
       </c>
       <c r="U2" t="n">
-        <v>6.7966</v>
+        <v>3.5865</v>
       </c>
       <c r="V2" t="n">
         <v>11.0767</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>11.003</v>
+        <v>13.6158</v>
       </c>
       <c r="E3" t="n">
-        <v>6.358000000000001</v>
+        <v>26.062</v>
       </c>
       <c r="F3" t="n">
-        <v>4.645099999999999</v>
+        <v>-12.4462</v>
       </c>
       <c r="G3" t="n">
-        <v>-34.5586</v>
+        <v>-32.724</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.9839</v>
+        <v>-0.6294999999999995</v>
       </c>
       <c r="I3" t="n">
-        <v>-21.5746</v>
+        <v>-32.0949</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.5306</v>
+        <v>24.4573</v>
       </c>
       <c r="K3" t="n">
-        <v>8.9953</v>
+        <v>28.3683</v>
       </c>
       <c r="L3" t="n">
-        <v>-10.5262</v>
+        <v>-3.911300000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-33.0281</v>
+        <v>-57.1814</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.9793</v>
+        <v>-28.9981</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.0482</v>
+        <v>-28.1838</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.649900000000001</v>
+        <v>-0.4551000000000006</v>
       </c>
       <c r="Q3" t="n">
-        <v>-54.8592</v>
+        <v>-74.8908</v>
       </c>
       <c r="R3" t="n">
-        <v>46.2094</v>
+        <v>74.4357</v>
       </c>
       <c r="S3" t="n">
-        <v>46.1289</v>
+        <v>1.6039</v>
       </c>
       <c r="T3" t="n">
-        <v>35.0078</v>
+        <v>2.194</v>
       </c>
       <c r="U3" t="n">
-        <v>11.1207</v>
+        <v>-0.5897999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>8.0829</v>
+        <v>45.191</v>
       </c>
       <c r="W3" t="n">
-        <v>27.74</v>
+        <v>74.30119999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.6571</v>
+        <v>-29.1102</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0807</v>
+        <v>2.7403</v>
       </c>
       <c r="E4" t="n">
-        <v>4.293600000000001</v>
+        <v>3.4854</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2128000000000001</v>
+        <v>-0.7450999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6414000000000002</v>
@@ -766,13 +766,13 @@
         <v>8.4224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8132</v>
+        <v>-0.5270999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7647999999999999</v>
+        <v>-0.04339999999999994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04840000000000011</v>
+        <v>-0.4837</v>
       </c>
       <c r="V4" t="n">
         <v>1.4051</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1841</v>
+        <v>2.248</v>
       </c>
       <c r="E5" t="n">
         <v>1.3549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8293</v>
+        <v>0.8931</v>
       </c>
       <c r="G5" t="n">
         <v>1.4418</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1976</v>
+        <v>0.2614</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1976</v>
+        <v>0.2614</v>
       </c>
       <c r="V5" t="n">
         <v>0.5447</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.325199999999999</v>
+        <v>0.2586</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8292</v>
+        <v>0.2586</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.5039</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-32.724</v>
+        <v>0.2586</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6294999999999995</v>
+        <v>0.2586</v>
       </c>
       <c r="I6" t="n">
-        <v>-32.0949</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>24.4573</v>
+        <v>0.2586</v>
       </c>
       <c r="K6" t="n">
-        <v>28.3683</v>
+        <v>0.2586</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.911300000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-57.1814</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-28.9981</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-28.1838</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4551000000000006</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-74.8908</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>74.4357</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.6865</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.038200000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.6478</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>45.191</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>74.30119999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-29.1102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>L. LANGARITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2586</v>
+        <v>0.1752</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2586</v>
+        <v>0.0172</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2586</v>
+        <v>0.1752</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2586</v>
+        <v>0.0172</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2586</v>
+        <v>0.0172</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2586</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. LANGARITA</t>
+          <t>A. SAVKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1752</v>
+        <v>-1.5284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0172</v>
+        <v>-0.8593</v>
       </c>
       <c r="F8" t="n">
+        <v>-0.6691</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3159</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.1579</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.1752</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0172</v>
-      </c>
       <c r="I8" t="n">
+        <v>-0.4738</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.7896</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.7896</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="N8" t="n">
         <v>0.1579</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.1579</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
-        <v>0.1579</v>
+        <v>0.3159</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.1231</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.0534</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SAVKOV</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5911</v>
+        <v>-1.7406</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8593</v>
+        <v>1.7733</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7318</v>
+        <v>-3.513800000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3159</v>
+        <v>-24.1899</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1579</v>
+        <v>-16.7888</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4738</v>
+        <v>-7.401400000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7896</v>
+        <v>5.6443</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.7599</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7896</v>
+        <v>3.8846</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4738</v>
+        <v>-29.8345</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1579</v>
+        <v>-18.5489</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3159</v>
+        <v>-11.2861</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>25.7228</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-17.7553</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>43.478</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1858</v>
+        <v>6.9126</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0697</v>
+        <v>5.7842</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1161</v>
+        <v>1.1286</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0895</v>
+        <v>-10.1855</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>8.0997</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0895</v>
+        <v>-18.285</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0751</v>
+        <v>-10.9279</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2951</v>
+        <v>8.7874</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.3701</v>
+        <v>-19.7155</v>
       </c>
       <c r="G11" t="n">
-        <v>-24.1899</v>
+        <v>-8.787400000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>-16.7888</v>
+        <v>3.4602</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.401400000000001</v>
+        <v>-12.247</v>
       </c>
       <c r="J11" t="n">
-        <v>5.6443</v>
+        <v>11.638</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7599</v>
+        <v>14.4121</v>
       </c>
       <c r="L11" t="n">
-        <v>3.8846</v>
+        <v>-2.7739</v>
       </c>
       <c r="M11" t="n">
-        <v>-29.8345</v>
+        <v>-20.4257</v>
       </c>
       <c r="N11" t="n">
-        <v>-18.5489</v>
+        <v>-10.9522</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.2861</v>
+        <v>-9.473100000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>25.7228</v>
+        <v>6.6015</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.7553</v>
+        <v>-13.6579</v>
       </c>
       <c r="R11" t="n">
-        <v>43.478</v>
+        <v>20.2595</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5787</v>
+        <v>7.7012</v>
       </c>
       <c r="T11" t="n">
-        <v>6.306500000000001</v>
+        <v>4.8863</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7277999999999998</v>
+        <v>2.8151</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.1855</v>
+        <v>-16.4433</v>
       </c>
       <c r="W11" t="n">
-        <v>8.0997</v>
+        <v>5.9207</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.285</v>
+        <v>-22.3641</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>J. RICHARDSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.055699999999999</v>
+        <v>-11.1715</v>
       </c>
       <c r="E12" t="n">
-        <v>4.315300000000001</v>
+        <v>-10.0329</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.370999999999999</v>
+        <v>-1.1387</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.234500000000001</v>
+        <v>-6.5892</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.8083</v>
+        <v>-6.005</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4262</v>
+        <v>-0.5840999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>4.0181</v>
+        <v>-4.9764</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1138</v>
+        <v>-5.6007</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9043</v>
+        <v>0.6242999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.2525</v>
+        <v>-1.6128</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.9218</v>
+        <v>-0.4042000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.3309</v>
+        <v>-1.2084</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.6014</v>
+        <v>-2.0488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.8526</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>15.2513</v>
+        <v>2.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>10.3638</v>
+        <v>-1.1346</v>
       </c>
       <c r="T12" t="n">
-        <v>9.978300000000001</v>
+        <v>-0.9788</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3853</v>
+        <v>-0.1559</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4162</v>
+        <v>-1.399</v>
       </c>
       <c r="W12" t="n">
-        <v>12.1717</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.7553</v>
+        <v>-2.1015</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5305</v>
+        <v>-11.279</v>
       </c>
       <c r="E13" t="n">
-        <v>15.0717</v>
+        <v>-2.3454</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.6021</v>
+        <v>-8.9337</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.787400000000002</v>
+        <v>-9.234500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4602</v>
+        <v>-6.8083</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.247</v>
+        <v>-2.4262</v>
       </c>
       <c r="J13" t="n">
-        <v>11.638</v>
+        <v>4.0181</v>
       </c>
       <c r="K13" t="n">
-        <v>14.4121</v>
+        <v>1.1138</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7739</v>
+        <v>2.9043</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.4257</v>
+        <v>-13.2525</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.9522</v>
+        <v>-7.9218</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.473100000000001</v>
+        <v>-5.3309</v>
       </c>
       <c r="P13" t="n">
-        <v>6.6015</v>
+        <v>-6.6014</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6579</v>
+        <v>-21.8526</v>
       </c>
       <c r="R13" t="n">
-        <v>20.2595</v>
+        <v>15.2513</v>
       </c>
       <c r="S13" t="n">
-        <v>13.099</v>
+        <v>3.1405</v>
       </c>
       <c r="T13" t="n">
-        <v>11.1713</v>
+        <v>3.3174</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9279</v>
+        <v>-0.177</v>
       </c>
       <c r="V13" t="n">
-        <v>-16.4433</v>
+        <v>1.4162</v>
       </c>
       <c r="W13" t="n">
-        <v>5.9207</v>
+        <v>12.1717</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.3641</v>
+        <v>-10.7553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.236299999999998</v>
+        <v>-14.4467</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0718</v>
+        <v>-14.0841</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.3081</v>
+        <v>-0.3625000000000009</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6143</v>
+        <v>-34.5586</v>
       </c>
       <c r="H14" t="n">
-        <v>8.209999999999999</v>
+        <v>-12.9839</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.595199999999999</v>
+        <v>-21.5746</v>
       </c>
       <c r="J14" t="n">
-        <v>10.8649</v>
+        <v>-1.5306</v>
       </c>
       <c r="K14" t="n">
-        <v>9.264099999999999</v>
+        <v>8.9953</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6012</v>
+        <v>-10.5262</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.2509</v>
+        <v>-33.0281</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0543</v>
+        <v>-21.9793</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.1965</v>
+        <v>-11.0482</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.2841</v>
+        <v>-8.649900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.3</v>
+        <v>-54.8592</v>
       </c>
       <c r="R14" t="n">
-        <v>10.0159</v>
+        <v>46.2094</v>
       </c>
       <c r="S14" t="n">
-        <v>12.3565</v>
+        <v>20.679</v>
       </c>
       <c r="T14" t="n">
-        <v>10.9824</v>
+        <v>14.5658</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3742</v>
+        <v>6.1133</v>
       </c>
       <c r="V14" t="n">
-        <v>-15.9229</v>
+        <v>8.0829</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5244</v>
+        <v>27.74</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.4473</v>
+        <v>-19.6571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RICHARDSON</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.8961</v>
+        <v>-14.9474</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.4753</v>
+        <v>-12.9772</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.421</v>
+        <v>-1.9703</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.5892</v>
+        <v>-8.109</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.005</v>
+        <v>-3.298</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5840999999999998</v>
+        <v>-4.811</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.9764</v>
+        <v>-2.5858</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.6007</v>
+        <v>0.5981999999999998</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6242999999999999</v>
+        <v>-3.1838</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6128</v>
+        <v>-5.523199999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4042000000000001</v>
+        <v>-3.8959</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2084</v>
+        <v>-1.6272</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0488</v>
+        <v>-5.4633</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.7803</v>
+        <v>-12.975</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7316</v>
+        <v>7.5119</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.8592</v>
+        <v>2.0882</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.421</v>
+        <v>0.4046999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4382</v>
+        <v>1.6835</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.399</v>
+        <v>-3.4637</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7025</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1015</v>
+        <v>-5.6427</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.801</v>
+        <v>-16.3755</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.069599999999999</v>
+        <v>-8.0831</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.7316</v>
+        <v>-8.292300000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-6.606</v>
@@ -1702,13 +1702,13 @@
         <v>5.007899999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0886</v>
+        <v>1.5142</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1422</v>
+        <v>2.1285</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0535</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-8.552100000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.3084</v>
+        <v>-16.573</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.7712</v>
+        <v>-0.4248000000000005</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5372</v>
+        <v>-16.1482</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.109</v>
+        <v>1.6143</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.298</v>
+        <v>8.209999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.811</v>
+        <v>-6.595199999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5858</v>
+        <v>10.8649</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5981999999999998</v>
+        <v>9.264099999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.1838</v>
+        <v>1.6012</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.523199999999999</v>
+        <v>-9.2509</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.8959</v>
+        <v>-1.0543</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6272</v>
+        <v>-8.1965</v>
       </c>
       <c r="P17" t="n">
-        <v>-5.4633</v>
+        <v>-7.2841</v>
       </c>
       <c r="Q17" t="n">
-        <v>-12.975</v>
+        <v>-17.3</v>
       </c>
       <c r="R17" t="n">
-        <v>7.5119</v>
+        <v>10.0159</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2727</v>
+        <v>5.019699999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.3894</v>
+        <v>3.4854</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1168</v>
+        <v>1.5344</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.4637</v>
+        <v>-15.9229</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1789</v>
+        <v>2.5244</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.6427</v>
+        <v>-18.4473</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.6613</v>
+        <v>-17.2455</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.625800000000001</v>
+        <v>-1.096500000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.0353</v>
+        <v>-16.1488</v>
       </c>
       <c r="G18" t="n">
         <v>-4.7069</v>
@@ -1858,13 +1858,13 @@
         <v>10.0159</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.0777</v>
+        <v>-0.662</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.6876</v>
+        <v>-0.1584999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.3898</v>
+        <v>-0.5034</v>
       </c>
       <c r="V18" t="n">
         <v>-7.0966</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.7716</v>
+        <v>-17.626</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0589</v>
+        <v>5.092899999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-22.7131</v>
+        <v>-22.7192</v>
       </c>
       <c r="G19" t="n">
-        <v>-17.9055</v>
+        <v>-9.8011</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6828000000000001</v>
+        <v>-14.8246</v>
       </c>
       <c r="I19" t="n">
-        <v>-17.2228</v>
+        <v>5.023200000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>10.7556</v>
+        <v>34.4057</v>
       </c>
       <c r="K19" t="n">
-        <v>11.3054</v>
+        <v>12.0572</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5494999999999995</v>
+        <v>22.3482</v>
       </c>
       <c r="M19" t="n">
-        <v>-28.6613</v>
+        <v>-44.2068</v>
       </c>
       <c r="N19" t="n">
-        <v>-11.9882</v>
+        <v>-26.8817</v>
       </c>
       <c r="O19" t="n">
-        <v>-16.6726</v>
+        <v>-17.3253</v>
       </c>
       <c r="P19" t="n">
-        <v>9.788399999999999</v>
+        <v>-6.3736</v>
       </c>
       <c r="Q19" t="n">
-        <v>-14.796</v>
+        <v>-64.8751</v>
       </c>
       <c r="R19" t="n">
-        <v>24.5844</v>
+        <v>58.5016</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.7962</v>
+        <v>-2.1271</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6917</v>
+        <v>4.0244</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.1047</v>
+        <v>-6.151899999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.8575</v>
+        <v>0.6762999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>4.6736</v>
+        <v>31.5383</v>
       </c>
       <c r="X19" t="n">
-        <v>-15.531</v>
+        <v>-30.8616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>-35.7781</v>
+        <v>-20.7302</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.995</v>
+        <v>1.6308</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.7828</v>
+        <v>-22.3612</v>
       </c>
       <c r="G20" t="n">
-        <v>-9.177099999999999</v>
+        <v>-17.9055</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9329</v>
+        <v>-0.6828000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.244299999999999</v>
+        <v>-17.2228</v>
       </c>
       <c r="J20" t="n">
-        <v>17.1451</v>
+        <v>10.7556</v>
       </c>
       <c r="K20" t="n">
-        <v>11.001</v>
+        <v>11.3054</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1441</v>
+        <v>-0.5494999999999995</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.3221</v>
+        <v>-28.6613</v>
       </c>
       <c r="N20" t="n">
-        <v>-12.9341</v>
+        <v>-11.9882</v>
       </c>
       <c r="O20" t="n">
-        <v>-13.388</v>
+        <v>-16.6726</v>
       </c>
       <c r="P20" t="n">
-        <v>-11.6093</v>
+        <v>9.788399999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-33.9172</v>
+        <v>-14.796</v>
       </c>
       <c r="R20" t="n">
-        <v>22.308</v>
+        <v>24.5844</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.4369</v>
+        <v>-1.755</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.7957</v>
+        <v>0.9976000000000002</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.6411</v>
+        <v>-2.7529</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5546</v>
+        <v>-10.8575</v>
       </c>
       <c r="W20" t="n">
-        <v>8.573</v>
+        <v>4.6736</v>
       </c>
       <c r="X20" t="n">
-        <v>-11.1277</v>
+        <v>-15.531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>-36.4325</v>
+        <v>-24.7937</v>
       </c>
       <c r="E21" t="n">
-        <v>-37.3126</v>
+        <v>-20.2059</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8805000000000004</v>
+        <v>-4.5879</v>
       </c>
       <c r="G21" t="n">
-        <v>-22.3893</v>
+        <v>11.9723</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.9721</v>
+        <v>5.832199999999998</v>
       </c>
       <c r="I21" t="n">
-        <v>-9.417100000000001</v>
+        <v>6.1403</v>
       </c>
       <c r="J21" t="n">
-        <v>16.5917</v>
+        <v>38.2207</v>
       </c>
       <c r="K21" t="n">
-        <v>10.5903</v>
+        <v>19.5094</v>
       </c>
       <c r="L21" t="n">
-        <v>6.0013</v>
+        <v>18.7113</v>
       </c>
       <c r="M21" t="n">
-        <v>-38.9806</v>
+        <v>-26.2483</v>
       </c>
       <c r="N21" t="n">
-        <v>-23.5622</v>
+        <v>-13.6768</v>
       </c>
       <c r="O21" t="n">
-        <v>-15.4188</v>
+        <v>-12.5712</v>
       </c>
       <c r="P21" t="n">
-        <v>-17.5274</v>
+        <v>-43.4776</v>
       </c>
       <c r="Q21" t="n">
-        <v>-68.517</v>
+        <v>-89.2316</v>
       </c>
       <c r="R21" t="n">
-        <v>50.9898</v>
+        <v>45.7538</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.507099999999999</v>
+        <v>-0.07810000000000011</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.206500000000001</v>
+        <v>-0.9056999999999997</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>0.8277000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>8.991</v>
+        <v>6.789400000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>21.8191</v>
+        <v>31.7111</v>
       </c>
       <c r="X21" t="n">
-        <v>-12.8282</v>
+        <v>-24.9216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>-38.2562</v>
+        <v>-25.8911</v>
       </c>
       <c r="E22" t="n">
-        <v>-27.1037</v>
+        <v>-26.3453</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.1524</v>
+        <v>0.4541000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>11.9723</v>
+        <v>-22.3893</v>
       </c>
       <c r="H22" t="n">
-        <v>5.832199999999998</v>
+        <v>-12.9721</v>
       </c>
       <c r="I22" t="n">
-        <v>6.1403</v>
+        <v>-9.417100000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>38.2207</v>
+        <v>16.5917</v>
       </c>
       <c r="K22" t="n">
-        <v>19.5094</v>
+        <v>10.5903</v>
       </c>
       <c r="L22" t="n">
-        <v>18.7113</v>
+        <v>6.0013</v>
       </c>
       <c r="M22" t="n">
-        <v>-26.2483</v>
+        <v>-38.9806</v>
       </c>
       <c r="N22" t="n">
-        <v>-13.6768</v>
+        <v>-23.5622</v>
       </c>
       <c r="O22" t="n">
-        <v>-12.5712</v>
+        <v>-15.4188</v>
       </c>
       <c r="P22" t="n">
-        <v>-43.4776</v>
+        <v>-17.5274</v>
       </c>
       <c r="Q22" t="n">
-        <v>-89.2316</v>
+        <v>-68.517</v>
       </c>
       <c r="R22" t="n">
-        <v>45.7538</v>
+        <v>50.9898</v>
       </c>
       <c r="S22" t="n">
-        <v>-13.5404</v>
+        <v>5.0347</v>
       </c>
       <c r="T22" t="n">
-        <v>-7.803900000000001</v>
+        <v>3.760699999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.7364</v>
+        <v>1.274</v>
       </c>
       <c r="V22" t="n">
-        <v>6.789400000000001</v>
+        <v>8.991</v>
       </c>
       <c r="W22" t="n">
-        <v>31.7111</v>
+        <v>21.8191</v>
       </c>
       <c r="X22" t="n">
-        <v>-24.9216</v>
+        <v>-12.8282</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>-40.5228</v>
+        <v>-27.2278</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.664300000000001</v>
+        <v>-10.027</v>
       </c>
       <c r="F23" t="n">
-        <v>-30.8583</v>
+        <v>-17.2008</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.8011</v>
+        <v>-9.177099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-14.8246</v>
+        <v>-1.9329</v>
       </c>
       <c r="I23" t="n">
-        <v>5.023200000000001</v>
+        <v>-7.244299999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>34.4057</v>
+        <v>17.1451</v>
       </c>
       <c r="K23" t="n">
-        <v>12.0572</v>
+        <v>11.001</v>
       </c>
       <c r="L23" t="n">
-        <v>22.3482</v>
+        <v>6.1441</v>
       </c>
       <c r="M23" t="n">
-        <v>-44.2068</v>
+        <v>-26.3221</v>
       </c>
       <c r="N23" t="n">
-        <v>-26.8817</v>
+        <v>-12.9341</v>
       </c>
       <c r="O23" t="n">
-        <v>-17.3253</v>
+        <v>-13.388</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.3736</v>
+        <v>-11.6093</v>
       </c>
       <c r="Q23" t="n">
-        <v>-64.8751</v>
+        <v>-33.9172</v>
       </c>
       <c r="R23" t="n">
-        <v>58.5016</v>
+        <v>22.308</v>
       </c>
       <c r="S23" t="n">
-        <v>-25.0244</v>
+        <v>-3.8869</v>
       </c>
       <c r="T23" t="n">
-        <v>-10.733</v>
+        <v>-1.8279</v>
       </c>
       <c r="U23" t="n">
-        <v>-14.2913</v>
+        <v>-2.059</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6762999999999999</v>
+        <v>-2.5546</v>
       </c>
       <c r="W23" t="n">
-        <v>31.5383</v>
+        <v>8.573</v>
       </c>
       <c r="X23" t="n">
-        <v>-30.8616</v>
+        <v>-11.1277</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>-222.5974</v>
+        <v>-192.5852</v>
       </c>
       <c r="E24" t="n">
-        <v>-54.8764</v>
+        <v>-43.0266</v>
       </c>
       <c r="F24" t="n">
-        <v>-167.7201</v>
+        <v>-149.5593</v>
       </c>
       <c r="G24" t="n">
         <v>-175.9901</v>
       </c>
       <c r="H24" t="n">
-        <v>-38.0248</v>
+        <v>-38.02479999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-137.965</v>
@@ -2308,7 +2308,7 @@
         <v>49.8333</v>
       </c>
       <c r="M24" t="n">
-        <v>-405.4647999999999</v>
+        <v>-405.4648</v>
       </c>
       <c r="N24" t="n">
         <v>-217.6656</v>
@@ -2317,25 +2317,25 @@
         <v>-187.7991</v>
       </c>
       <c r="P24" t="n">
-        <v>-71.7025</v>
+        <v>-71.70250000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-589.5662</v>
+        <v>-589.5661999999999</v>
       </c>
       <c r="R24" t="n">
         <v>517.8638</v>
       </c>
       <c r="S24" t="n">
-        <v>18.4886</v>
+        <v>48.4994</v>
       </c>
       <c r="T24" t="n">
-        <v>31.28510000000001</v>
+        <v>43.13189999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-12.7951</v>
+        <v>5.367200000000002</v>
       </c>
       <c r="V24" t="n">
-        <v>6.608599999999997</v>
+        <v>6.608599999999996</v>
       </c>
       <c r="W24" t="n">
         <v>273.9317</v>
